--- a/01-Planejamento/03-Estrategia_e_Plano/04-Matriz_Planejamento/matriz_verificaca_evidencias.xlsx
+++ b/01-Planejamento/03-Estrategia_e_Plano/04-Matriz_Planejamento/matriz_verificaca_evidencias.xlsx
@@ -9,10 +9,14 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_Checklists" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_Checklists" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Checklists" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Checklists" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q1_Checklists'!$A$1:$F$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2_Checklists'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Q3_Checklists'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Q4_Checklists'!$A$1:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1399,4 +1403,987 @@
   <autoFilter ref="A1:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
+    <col width="130" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_avaliacao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>questao_auditoria</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>situacao_encontrada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>item_evidencia</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>descricao_avaliacao</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="210" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.2-q2703evi</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S3.2 - A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>q2703evi</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova definição documentada do quantitativo necessário de pessoal de TIC/SI com base em critérios ou procedimentos técnicos.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.2-q2703evi.
+Objetivo da avaliação: verificar se a evidência comprova definição documentada do quantitativo necessário de pessoal de TIC e segurança da informação com base em critérios ou procedimentos técnicos.
+Contexto da situação encontrada: S3.2 - A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.
+Item de evidência avaliado: q2703evi.
+Evidência esperada no questionário: política ou metodologia de dimensionamento; estudos ou relatórios técnicos; definição documentada do quantitativo necessário; critérios utilizados, como serviços, sistemas, demanda, riscos ou complexidade; revisões periódicas; planos de provimento; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C2 - COBIT 2019 APO07.01; C5 - COBIT 2019 APO07.05; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
+2. Verifique se a evidência se refere à organização auditada e ao período ou contexto avaliado.
+3. Verifique se há definição do quantitativo necessário de pessoal de TIC e de segurança da informação, e não apenas relação do quadro atual.
+4. Verifique se o dimensionamento está baseado em critérios ou procedimentos técnicos, como porte, serviços, sistemas, demandas, riscos, contratos ou complexidade.
+5. Verifique se a evidência indica abrangência, premissas, unidade responsável ou processo de revisão do dimensionamento.
+6. Verifique se a evidência é compatível com as respostas declaradas em q2703ext[B] e q2703ext[C].
+7. Decida se a evidência comprova, de forma suficiente, a definição documentada do quantitativo necessário de pessoal de TIC/SI.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.2-q2703evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="210" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.4-q2701evi</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>q2701evi</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova perfis profissionais definidos para gestores de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.4-q2701evi.
+Objetivo da avaliação: verificar se a evidência comprova perfis profissionais definidos e documentados para gestores de TIC e segurança da informação.
+Contexto da situação encontrada: S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.
+Item de evidência avaliado: q2701evi.
+Evidência esperada no questionário: normativos ou documentos com atribuições e competências; descrições de cargos ou funções; matrizes de competências; registros de revisão periódica; publicações em portal institucional ou transparência ativa; atos de designação; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
+2. Verifique se o documento define responsabilidades e atribuições de gestores de TIC ou segurança da informação.
+3. Verifique se o documento relaciona competências, habilidades, experiência ou requisitos mínimos esperados para os gestores.
+4. Verifique se os perfis são aplicáveis à organização auditada e às funções de gestão avaliadas.
+5. Verifique se há indício de publicação, comunicação, revisão periódica ou uso institucional dos perfis.
+6. Verifique se a evidência é compatível com as respostas declaradas em q2701ext[A] e q2701ext[C].
+7. Decida se a evidência comprova, de forma suficiente, perfis profissionais definidos para gestores de TIC/SI.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.4-q2701evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="210" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.4-q2702evi</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>q2702evi</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova perfis profissionais definidos para colaboradores de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.4-q2702evi.
+Objetivo da avaliação: verificar se a evidência comprova perfis profissionais definidos e documentados para colaboradores de TIC e segurança da informação.
+Contexto da situação encontrada: S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.
+Item de evidência avaliado: q2702evi.
+Evidência esperada no questionário: descrições de cargos ou funções; matrizes de competências; normativos com atribuições e responsabilidades; registros de revisão periódica; publicações em portal institucional ou mecanismos de transparência; planos de capacitação relacionados; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
+2. Verifique se o documento define responsabilidades e atribuições de colaboradores, ocupações ou grupos de ocupações de TIC/SI.
+3. Verifique se o documento relaciona competências, habilidades, experiência ou requisitos mínimos esperados para os colaboradores.
+4. Verifique se os perfis abrangem funções essenciais de TIC, segurança da informação ou sustentação tecnológica compatíveis com o escopo da organização.
+5. Verifique se há indício de publicação, comunicação, revisão periódica ou uso institucional dos perfis.
+6. Verifique se a evidência é compatível com as respostas declaradas em q2702ext[A] e q2702ext[C].
+7. Decida se a evidência comprova, de forma suficiente, perfis profissionais definidos para colaboradores de TIC/SI.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.4-q2702evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="210" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.4-q2704evi</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>q2704evi</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova que a escolha de gestores de TIC/SI utiliza perfis profissionais previamente definidos.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.4-q2704evi.
+Objetivo da avaliação: verificar se a evidência comprova que a escolha de gestores de TIC e segurança da informação ocorre segundo perfis profissionais previamente definidos e documentados.
+Contexto da situação encontrada: S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.
+Item de evidência avaliado: q2704evi.
+Evidência esperada no questionário: perfis profissionais documentados; critérios de seleção; registros de avaliação prévia de impedimentos legais; utilização de entrevistas, análises curriculares ou outras ferramentas estruturadas; currículos publicados; atos de designação; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C2 - COBIT 2019 APO07.01; C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
+2. Verifique se há perfis profissionais previamente definidos para os cargos ou funções de gestão avaliados.
+3. Verifique se a escolha ou designação de gestores considera perfil profissional, competências, experiência ou requisitos documentados.
+4. Verifique se há registros de aplicação do critério, como avaliação curricular, ferramenta estruturada, justificativa de designação ou ato formal.
+5. Verifique se a evidência permite vincular o gestor ou função avaliada à organização auditada.
+6. Verifique se a evidência é compatível com a resposta declarada em q2704ext[B].
+7. Decida se a evidência comprova, de forma suficiente, o uso de perfis previamente definidos na escolha de gestores de TIC/SI.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.4-q2704evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="210" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.5-q2705evi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>q2705evi</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova identificação documentada de lacunas de competências de gestores, colaboradores de TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.5-q2705evi.
+Objetivo da avaliação: verificar se a evidência comprova identificação documentada de lacunas de competências de gestores, colaboradores de TIC e segurança da informação.
+Contexto da situação encontrada: S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.
+Item de evidência avaliado: q2705evi.
+Evidência esperada no questionário: matrizes de competências; avaliações de perfil; levantamentos de necessidades de capacitação; diagnósticos de competências técnicas e gerenciais; planos de desenvolvimento; relatórios ou registros documentados; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusula 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controle 6.3.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
+2. Verifique se a evidência identifica lacunas de competências de liderança, gestão, TIC ou segurança da informação.
+3. Verifique se o diagnóstico contempla colaboradores e/ou gestores compatíveis com o escopo declarado pela organização.
+4. Verifique se há método, matriz, levantamento, avaliação ou critério documentado para identificar as lacunas.
+5. Verifique se a evidência indica data, período, responsáveis ou abrangência suficiente para demonstrar uso institucional.
+6. Verifique se a evidência é compatível com as respostas declaradas em q2705ext[B], q2705ext[C] e q2705ext[D].
+7. Decida se a evidência comprova, de forma suficiente, a identificação documentada de lacunas de competências em TIC/SI.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.5-q2705evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="210" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.5-q2706evi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>q2706evi</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova tratamento das lacunas de competências em TIC e segurança da informação.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.5-q2706evi.
+Objetivo da avaliação: verificar se a evidência comprova tratamento das lacunas de competências dos colaboradores e gestores de TIC e segurança da informação.
+Contexto da situação encontrada: S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.
+Item de evidência avaliado: q2706evi.
+Evidência esperada no questionário: plano de capacitação ou treinamento; registros de participação em cursos e treinamentos; ações de incentivo à capacitação; acompanhamento de participação e resultados; revisões periódicas do plano de capacitação; contratações ou apoio especializado; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusula 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controle 6.3.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
+2. Verifique se a evidência apresenta plano, ações ou mecanismos de tratamento de lacunas de competências em TIC/SI.
+3. Verifique se há ações de capacitação, realocação, provimento, contratação, apoio especializado ou desenvolvimento compatíveis com as lacunas identificadas.
+4. Verifique se há incentivo, monitoramento de participação, acompanhamento de resultados ou revisão periódica do plano de capacitação.
+5. Verifique se a evidência indica data, período, responsáveis ou abrangência suficiente para demonstrar execução institucional.
+6. Verifique se a evidência é compatível com as respostas declaradas em q2706ext[A], q2706ext[B] e q2706ext[C].
+7. Decida se a evidência comprova, de forma suficiente, o tratamento das lacunas de competências em TIC/SI.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.5-q2706evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="210" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.6-q2703evi</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>q2703evi</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência de dimensionamento de pessoal demonstra capacidade interna mínima para coordenar e fiscalizar TIC em modelo terceirizado ou externo.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.6-q2703evi.
+Objetivo da avaliação: verificar se a evidência de dimensionamento de pessoal demonstra capacidade interna mínima para coordenação, planejamento, aprovação técnica e fiscalização de TIC quando houver dependência relevante de terceiros ou estrutura externa.
+Contexto da situação encontrada: S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.
+Item de evidência avaliado: q2703evi.
+Evidência esperada no questionário: política ou metodologia de dimensionamento; estudos ou relatórios técnicos; definição documentada do quantitativo necessário; critérios utilizados, como serviços, sistemas, demanda, riscos ou complexidade; revisões periódicas; planos de provimento; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C2 - COBIT 2019 APO07.01; C5 - COBIT 2019 APO07.05; C6 - COBIT 2019 APO07.06; C8 - COBIT 2019 DSS01.02.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
+2. Verifique se a evidência considera a dependência de terceiros, estrutura externa, contratos ou serviços críticos de TIC no dimensionamento de pessoal.
+3. Verifique se há capacidade interna prevista para coordenação, planejamento, aprovação técnica, fiscalização contratual ou retenção de conhecimento.
+4. Verifique se o quantitativo necessário é definido com base em critérios técnicos e não apenas em quadro existente ou disponibilidade orçamentária genérica.
+5. Verifique se a evidência é compatível com o modelo declarado em q0101 e com as respostas q2703ext[B] e q2703ext[C].
+6. Verifique se a evidência reduz o risco de dependência excessiva de fornecedores ou estrutura externa sem governabilidade interna.
+7. Decida se a evidência comprova, de forma suficiente, capacidade interna mínima planejada para coordenar e fiscalizar TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.6-q2703evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="210" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.6-q2801evi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>q2801evi</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova processo e artefatos de gestão e fiscalização contratual de TIC com papéis, responsabilidades e controles suficientes.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.6-q2801evi.
+Objetivo da avaliação: verificar se a evidência comprova processo e artefatos de gestão e fiscalização contratual de TIC capazes de assegurar coordenação, fiscalização e responsabilização interna sobre terceiros.
+Contexto da situação encontrada: S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.
+Item de evidência avaliado: q2801evi.
+Evidência esperada no questionário: manuais, fluxos, normas ou procedimentos internos; modelos padronizados de documentos; checklists; definição de papéis e responsabilidades; fluxogramas; instruções de trabalho; artefatos de planejamento da contratação; processos de fiscalização contratual; referências à Lei 14.133/2021 e normativos correlatos; ou outras evidências cabíveis, indicando a abrangência na organização.
+Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C6 - COBIT 2019 APO07.06; C7 - COBIT 2019 APO10.04; C8 - COBIT 2019 DSS01.02.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
+2. Verifique se o processo de gestão e fiscalização de contratos de TIC define etapas, responsáveis, papéis e controles.
+3. Verifique se há artefatos padronizados para fiscalização, como plano de fiscalização, termos de recebimento, relatórios, registros de ocorrências ou avaliação de desempenho.
+4. Verifique se os papéis internos são suficientes para supervisionar fornecedores e preservar responsabilização da organização.
+5. Verifique se o processo contempla gestão de riscos, conformidade, desempenho ou transferência/retenção de conhecimento quando aplicável.
+6. Verifique se a evidência é compatível com as respostas declaradas em q2801ext[E] e q2801ext[F].
+7. Decida se a evidência comprova, de forma suficiente, processo e artefatos de gestão e fiscalização contratual de TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.6-q2801evi",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="210" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q3-S3.6-q2804eviA</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>q2804eviA</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova aprovação técnica da área de TIC em norma regulamentadora e em caso concreto de contratação.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
+ID da avaliação: Q3-S3.6-q2804eviA.
+Objetivo da avaliação: verificar se a evidência comprova que contratações de soluções de TIC são submetidas à análise prévia e aprovação técnica da área de gestão de TIC, com norma regulamentadora e caso concreto.
+Contexto da situação encontrada: S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.
+Item de evidência avaliado: q2804eviA.
+Evidência esperada no questionário: norma regulamentando o processo de análise prévia e aprovação técnica da área de gestão de TIC e evidência de um caso concreto de contratação em que essa aprovação tenha ocorrido.
+Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C6 - COBIT 2019 APO07.06; C7 - COBIT 2019 APO10.04; C8 - COBIT 2019 DSS01.02.
+Checklist obrigatório:
+1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
+2. Verifique se há norma, fluxo, procedimento ou instrumento equivalente que exija análise prévia e aprovação técnica pela área de TIC.
+3. Verifique se há evidência de caso concreto em que a área de TIC realizou análise ou aprovação técnica de contratação de solução de TIC.
+4. Verifique se a aprovação técnica é atribuída à área de gestão de TIC ou responsável técnico interno, e não apenas ao fornecedor ou área demandante.
+5. Verifique se a evidência permite vincular a contratação e a aprovação técnica à organização auditada.
+6. Verifique se a evidência é compatível com a resposta declarada em q2804[A].
+7. Decida se a evidência comprova, de forma suficiente, aprovação técnica interna de TIC em norma e em caso concreto.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "id_avaliacao": "Q3-S3.6-q2804eviA",
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F10"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="120" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_avaliacao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>questao_auditoria</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>situacao_encontrada</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>item_evidencia</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>descricao_avaliacao</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>prompt_checklist</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.1-q2201evi</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S4.1 - Inexist?ncia, desatualiza??o, indisponibilidade ou insufici?ncia do cat?logo de servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>q2201evi</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova cat?logo de servi?os de TIC vigente, atualizado, acess?vel e aderente aos servi?os efetivamente prestados.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2201evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.1 - Inexist?ncia, desatualiza??o, indisponibilidade ou insufici?ncia do cat?logo de servi?os de TIC.
+Item de evid?ncia: q2201evi.
+Evid?ncia esperada no question?rio: evid?ncia do cat?logo e da gest?o de n?veis de servi?o, como cat?logo de servi?os vigente, ANS firmados, defini??o de metas, registros de monitoramento, relat?rios de desempenho, canais de atendimento definidos ou evid?ncias equivalentes, indicando a abrang?ncia na organiza??o.
+Crit?rios aplic?veis da matriz: C1 - ITIL 4, gerenciamento do cat?logo de servi?os; C2 - COBIT 2019, APO09.02, catalogar servi?os facilitados por TI.
+Checklist objetivo:
+1. Verificar se h? cat?logo de servi?os de TIC em documento, portal, sistema ou instrumento equivalente.
+2. Verificar se o cat?logo identifica servi?os efetivamente prestados pela ?rea de TIC e n?o apenas uma lista gen?rica de atividades.
+3. Verificar se o cat?logo cont?m informa??es m?nimas para solicita??o ou uso dos servi?os, como descri??o, p?blico-alvo, canal de atendimento, ponto de contato, prazo, hor?rio de suporte ou meta aplic?vel.
+4. Verificar se h? indica??o de atualiza??o, vig?ncia ou compatibilidade com os servi?os e acordos de n?vel de servi?o declarados.
+5. Verificar se a evid?ncia demonstra disponibilidade ou acessibilidade do cat?logo aos usu?rios, ?reas demandantes ou equipes de suporte.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.1-q2201evi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="110" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.2-q2201evi</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>S4.2 - Inexist?ncia de ANS, metas m?nimas ou monitoramento de n?veis de servi?o para os principais servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>q2201evi</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova ANS, metas m?nimas e monitoramento de n?veis de servi?o para os principais servi?os de TIC.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2201evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.2 - Inexist?ncia de ANS, metas m?nimas ou monitoramento de n?veis de servi?o para os principais servi?os de TIC.
+Item de evid?ncia: q2201evi.
+Evid?ncia esperada no question?rio: evid?ncia do cat?logo e da gest?o de n?veis de servi?o, como cat?logo de servi?os vigente, ANS firmados, defini??o de metas, registros de monitoramento, relat?rios de desempenho, canais de atendimento definidos ou evid?ncias equivalentes, indicando a abrang?ncia na organiza??o.
+Crit?rios aplic?veis da matriz: C2 - COBIT 2019, APO09.02, catalogar servi?os facilitados por TI; C3 - ITIL 4, gerenciamento de n?vel de servi?o.
+Checklist objetivo:
+1. Verificar se h? ANS, metas m?nimas, indicadores ou par?metros objetivos de atendimento para servi?os de TIC relevantes.
+2. Verificar se os n?veis de servi?o ou metas est?o associados a servi?os identific?veis e a ?reas usu?rias ou clientes internos.
+3. Verificar se h? registros de monitoramento peri?dico, relat?rios, pain?is, atas ou evid?ncias equivalentes sobre cumprimento dos n?veis de servi?o.
+4. Verificar se a evid?ncia permite identificar resultados, desvios, descumprimentos ou medidas de acompanhamento.
+5. Verificar se a evid?ncia ? compat?vel com a resposta declarat?ria e demonstra abrang?ncia suficiente na organiza??o.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.2-q2201evi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="110" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.3-q2203evi</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>q2203evi</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova invent?rio atualizado de ativos e servi?os de TI no contexto da gest?o de configura??o e ativos.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2203evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC.
+Item de evid?ncia: q2203evi.
+Evid?ncia esperada no question?rio: evid?ncia da gest?o de configura??o e ativos, como invent?rio atualizado de ativos e servi?os de TI, CMDB ou base equivalente, relacionamentos entre sistemas, infraestrutura e servi?os, uso dessas informa??es em mudan?as, norma ou procedimento formal, relat?rios ou ferramentas de controle.
+Crit?rios aplic?veis da matriz: C4 - ITIL 4, gerenciamento de ativos de TI; C5 - ITIL 4, gerenciamento de configura??o de servi?o.
+Checklist objetivo:
+1. Verificar se h? invent?rio ou base consolidada de ativos de TIC, servi?os de TI ou itens de configura??o relevantes.
+2. Verificar se o invent?rio cont?m elementos m?nimos como identifica??o do ativo, tipo, servi?o relacionado, respons?vel, localiza??o, ambiente, sistema, software, equipamento ou componente de infraestrutura.
+3. Verificar se a evid?ncia indica atualiza??o, manuten??o peri?dica ou uso operacional da base.
+4. Verificar se a evid?ncia demonstra relacionamento entre ativos, sistemas, infraestrutura e servi?os, quando aplic?vel.
+5. Verificar se a abrang?ncia ? suficiente para os principais servi?os ou ativos de TIC da organiza??o.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.3-q2203evi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.3-q2501evi</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>q2501evi</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova invent?rio de ativos associados ? informa??o e defini??o de respons?veis por ativos relevantes.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2501evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC.
+Item de evid?ncia: q2501evi.
+Evid?ncia esperada no question?rio: evid?ncia da gest?o de ativos associados ? informa??o, como invent?rio de ativos e informa??es cr?ticas, defini??o formal de respons?veis, identifica??o de informa??es cr?ticas, controles de prote??o, norma ou procedimento formal e relat?rios de acompanhamento.
+Crit?rios aplic?veis da matriz: C4 - ITIL 4, gerenciamento de ativos de TI.
+Checklist objetivo:
+1. Verificar se h? invent?rio de ativos associados ? informa??o, tais como sistemas, bases de dados, documentos digitais, backups, equipamentos ou outros ativos que armazenem, processem ou transmitam informa??es.
+2. Verificar se o invent?rio identifica ativos ou informa??es cr?ticas, sens?veis ou relevantes para os servi?os da organiza??o.
+3. Verificar se h? respons?veis formalmente definidos pelos ativos ou pelo processo de gest?o dos ativos.
+4. Verificar se a evid?ncia indica atualiza??o, revis?o ou acompanhamento do invent?rio.
+5. Verificar se a evid?ncia ? documental e suficiente, e n?o apenas declara??o gen?rica de que o processo existe.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.3-q2501evi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.3-q2504evi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>q2504evi</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova invent?rio e controle de dispositivos e softwares conectados ? rede ou usados nos servi?os de TIC.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2504evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC.
+Item de evid?ncia: q2504evi.
+Evid?ncia esperada no question?rio: evid?ncia da gest?o da seguran?a dos recursos de processamento da informa??o, incluindo invent?rio de dispositivos e softwares, registros de controle, relat?rios, ferramentas ou outros documentos que demonstrem abrang?ncia na organiza??o.
+Crit?rios aplic?veis da matriz: C4 - ITIL 4, gerenciamento de ativos de TI.
+Checklist objetivo:
+1. Verificar se h? invent?rio ou controle de dispositivos conectados ? rede, equipamentos, servidores, esta??es, recursos de nuvem ou componentes equivalentes.
+2. Verificar se h? invent?rio ou controle de softwares instalados, aplica??es, licen?as ou sistemas relevantes.
+3. Verificar se a evid?ncia cont?m dados suficientes para identifica??o, controle e atualiza??o dos ativos.
+4. Verificar se a evid?ncia demonstra abrang?ncia compat?vel com os principais ambientes ou servi?os de TIC.
+5. Desconsiderar controles de seguran?a n?o relacionados ao invent?rio quando eles n?o comprovarem identifica??o e controle de ativos.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.3-q2504evi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.4-q2203evi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>S4.4 - Aus?ncia ou fragilidade do processo de gest?o de configura??o</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>q2203evi</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova processo formal ou mecanismo equivalente de gest?o de configura??o e seus relacionamentos.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2203evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.4 - Aus?ncia ou fragilidade do processo de gest?o de configura??o.
+Item de evid?ncia: q2203evi.
+Evid?ncia esperada no question?rio: evid?ncia da gest?o de configura??o e ativos, como invent?rio atualizado de ativos e servi?os de TI, CMDB ou base equivalente, relacionamentos entre sistemas, infraestrutura e servi?os, uso dessas informa??es em mudan?as, norma ou procedimento formal, relat?rios ou ferramentas de controle.
+Crit?rios aplic?veis da matriz: C5 - ITIL 4, gerenciamento de configura??o de servi?o; C6 - COBIT 2019, BAI10.01, estabelecer e manter modelo de configura??o.
+Checklist objetivo:
+1. Verificar se h? norma, procedimento, guia, fluxo, pol?tica, ferramenta ou mecanismo equivalente para gest?o de configura??o.
+2. Verificar se a evid?ncia define ou demonstra itens de configura??o, atributos m?nimos, relacionamentos e respons?veis.
+3. Verificar se h? CMDB, base de configura??o, invent?rio estruturado ou ferramenta equivalente mantida pela organiza??o.
+4. Verificar se a base de configura??o ? usada ou referenciada em mudan?as, opera??o, an?lise de impacto ou gest?o dos servi?os.
+5. Verificar se a evid?ncia ? suficiente para comprovar processo executado ou mecanismo operacional, e n?o apenas inten??o futura.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.4-q2203evi".</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="110" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q4-S4.5-q2204evi</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gest?o de Servi?os de TIC</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>S4.5 - Inexist?ncia ou fragilidade do processo de gest?o de incidentes de TIC</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>q2204evi</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evid?ncia comprova processo formal, registros rastre?veis e tratamento estruturado de incidentes de servi?os e de seguran?a da informa??o.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2204evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
+Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
+Situa??o encontrada avaliada: S4.5 - Inexist?ncia ou fragilidade do processo de gest?o de incidentes de TIC.
+Item de evid?ncia: q2204evi.
+Evid?ncia esperada no question?rio: evid?ncia da gest?o de incidentes, como norma ou procedimento formal, registros de incidentes, chamados ou tickets, crit?rios de prioriza??o e escalonamento, base de conhecimento, relat?rios de atendimento, tratamento de incidentes de seguran?a, an?lise de causa raiz e a??es corretivas.
+Crit?rios aplic?veis da matriz: C7 - ITIL 4, gerenciamento de incidentes; C8 - COBIT 2019, DSS02.02, DSS02.04 e DSS02.07, requisi??es de servi?o e incidentes gerenciados.
+Checklist objetivo:
+1. Verificar se h? norma, procedimento, fluxo ou instrumento equivalente que formalize pap?is, responsabilidades, prioriza??o e escalamento de incidentes.
+2. Verificar se existem registros rastre?veis de incidentes, chamados, tickets, hist?rico de atendimento, respons?veis, datas, status e solu??o aplicada.
+3. Verificar se a resolu??o dos incidentes considera n?veis de servi?o, criticidade, impacto ou crit?rios objetivos de atendimento.
+4. Verificar se h? tratamento de incidentes de seguran?a da informa??o, com notifica??o, resposta, comunica??o ou responsabilidades definidas.
+5. Verificar se h? an?lise posterior de incidentes relevantes ou recorrentes, causa raiz, base de conhecimento, a??es corretivas ou evid?ncias equivalentes.
+Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
+O campo "id_avaliacao" deve ser "Q4-S4.5-q2204evi".</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F8"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/01-Planejamento/03-Estrategia_e_Plano/04-Matriz_Planejamento/matriz_verificaca_evidencias.xlsx
+++ b/01-Planejamento/03-Estrategia_e_Plano/04-Matriz_Planejamento/matriz_verificaca_evidencias.xlsx
@@ -7,16 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q1_Checklists" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q2_Checklists" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q3_Checklists" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Q4_Checklists" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Avaliacoes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Q1_Checklists'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Q2_Checklists'!$A$1:$F$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Q3_Checklists'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Q4_Checklists'!$A$1:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Avaliacoes'!$A$1:$F$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,12 +62,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -441,50 +438,50 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
     <col width="78" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="130" customWidth="1" min="6" max="6"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
+    <col width="120" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>id_avaliacao</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>questao_auditoria</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>situacao_encontrada</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>item_evidencia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>descricao_avaliacao</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>prompt_checklist</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="210" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.1-q0101evi</t>
@@ -512,13 +509,10 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.1-q0101evi.
-Objetivo da avaliação: verificar se a evidência comprova a formalização institucional da área, unidade, setor ou função de TIC da organização.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova formalização institucional da área, unidade, setor ou função de TIC.
 Contexto da situação encontrada: S1.1 - Ausência de formalização da área, unidade, setor ou função de TIC da organização.
-Item de evidência avaliado: q0101evi.
 Evidência esperada no questionário: lei, decreto, portaria, regimento interno, organograma, contrato, convênio, termo de cooperação ou instrumento equivalente que demonstre o modelo de organização e prestação dos serviços de TI.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.04; C5 - COBIT 2019 APO01.09; C9 - ABNT NBR ISO/IEC 38500:2025, item 5.6.1.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento identifica área, unidade, setor, função ou estrutura responsável por TIC.
@@ -531,21 +525,20 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.1-q0101evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="210" customHeight="1">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.2-q0103evi</t>
@@ -573,13 +566,10 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.2-q0103evi.
-Objetivo da avaliação: verificar se a evidência comprova atribuições formais suficientes da área de TIC, especialmente governança, planejamento ou gestão de TIC.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova atribuições formais suficientes da área de TIC.
 Contexto da situação encontrada: S1.2 - Área de TIC sem atribuições formais suficientes para planejamento, coordenação, gestão, execução, monitoramento e controle da TIC.
-Item de evidência avaliado: q0103evi.
 Evidência esperada no questionário: regimento interno, decreto, resolução, portaria, manual de competências, descrição formal de responsabilidades ou outras evidências cabíveis das atribuições formalizadas da área de TI.
-Critérios da matriz aplicáveis: C2 - COBIT 2019 APO01.05; C5 - COBIT 2019 APO01.09; C9 - ABNT NBR ISO/IEC 38500:2025, item 5.6.1.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento define atribuições ou competências da área de TIC.
@@ -593,21 +583,20 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.2-q0103evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="210" customHeight="1">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.3-q0102evi</t>
@@ -635,13 +624,10 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.3-q0102evi.
-Objetivo da avaliação: verificar se a evidência comprova o posicionamento hierárquico formal da área de TIC.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova o posicionamento hierárquico da área de TIC.
 Contexto da situação encontrada: S1.3 - Posicionamento organizacional inadequado da área de TIC.
-Item de evidência avaliado: q0102evi.
 Evidência esperada no questionário: organograma institucional, regimento interno, lei, decreto, portaria ou instrumento equivalente que demonstre a posição hierárquica da área de TI.
-Critérios da matriz aplicáveis: C3 - COBIT 2019 APO01.06; C4 - COBIT 2019 EDM01.02; C9 - ABNT NBR ISO/IEC 38500:2025, item 5.6.1.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento identifica a área de TIC e sua vinculação hierárquica.
@@ -654,21 +640,20 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.3-q0102evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="210" customHeight="1">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.4-q1001evi</t>
@@ -696,13 +681,10 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.4-q1001evi.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
 Objetivo da avaliação: verificar se a evidência comprova modelo básico de governança e gestão de TIC estabelecido pela alta administração.
 Contexto da situação encontrada: S1.4 - Ausência ou insuficiência de modelo básico de governança e gestão de TIC com papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.
-Item de evidência avaliado: q1001evi.
 Evidência esperada no questionário: política ou norma de governança de TI aprovada pela alta administração; regimento do comitê de TI e atas que comprovem sua atuação; organograma com papéis e responsabilidades; designação formal de gestores de sistemas; diretrizes de planejamento, riscos e desempenho de TI; documentos com objetivos, indicadores e metas de TI; ou outras evidências cabíveis.
-Critérios da matriz aplicáveis: C4 - COBIT 2019 EDM01.02; C5 - COBIT 2019 APO01.09; C6 - COBIT 2019 MEA01.04; C7 - Decreto nº 9.203/2017, art. 6º; C9 - ABNT NBR ISO/IEC 38500:2025, item 5.6.1; C10 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.1.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele foi aprovado ou estabelecido por autoridade competente ou alta administração.
 2. Verifique se o documento define diretrizes, estruturas, papéis ou responsabilidades para governança e gestão de TIC.
@@ -716,21 +698,20 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.4-q1001evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="210" customHeight="1">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.4-q1002evi</t>
@@ -758,13 +739,10 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.4-q1002evi.
-Objetivo da avaliação: verificar se a evidência comprova monitoramento do desempenho da gestão de TIC pela alta administração ou instância competente.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova monitoramento do desempenho da gestão de TIC.
 Contexto da situação encontrada: S1.4 - Ausência ou insuficiência de modelo básico de governança e gestão de TIC com papéis, responsabilidades, objetivos, indicadores, metas ou acompanhamento.
-Item de evidência avaliado: q1002evi.
 Evidência esperada no questionário: norma ou procedimento que estabeleça rotinas de monitoramento; painel ou sistema com indicadores e metas de TI; relatórios periódicos de desempenho; atas de reuniões da alta administração ou comitê de TI com análise de resultados; evidências de acompanhamento do plano de TI; ou outras evidências cabíveis.
-Critérios da matriz aplicáveis: C6 - COBIT 2019 MEA01.04; C7 - Decreto nº 9.203/2017, art. 6º; C9 - ABNT NBR ISO/IEC 38500:2025, item 5.6.1; C10 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.1.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal, gerencial ou institucional.
 2. Verifique se há rotina definida de monitoramento do desempenho da gestão de TIC.
@@ -777,21 +755,20 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.4-q1002evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="210" customHeight="1">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.5-q1001evi</t>
@@ -819,13 +796,10 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.5-q1001evi.
-Objetivo da avaliação: verificar se a evidência comprova a instituição formal de Comitê de TIC ou instância colegiada equivalente.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova instituição formal de Comitê de TIC ou instância equivalente.
 Contexto da situação encontrada: S1.5 - Ausência de Comitê de TIC ou instância equivalente formalmente instituído.
-Item de evidência avaliado: q1001evi.
 Evidência esperada no questionário: política ou norma de governança de TI, regimento do comitê de TI, ato constitutivo, composição, competências, atas ou outras evidências cabíveis sobre instância colegiada de TIC.
-Critérios da matriz aplicáveis: C2 - COBIT 2019 APO01.05; C4 - COBIT 2019 EDM01.02; C7 - Decreto nº 9.203/2017, art. 6º; C8 - Decreto nº 12.198/2024, art. 5º; C9 - ABNT NBR ISO/IEC 38500:2025, item 5.6.1; C10 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.1.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento institui Comitê de TIC ou instância colegiada equivalente.
@@ -839,21 +813,20 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.5-q1001evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="210" customHeight="1">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Q1-S1.6-q1001evi</t>
@@ -881,13 +854,10 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q1-S1.6-q1001evi.
-Objetivo da avaliação: verificar se a evidência comprova atuação efetiva do Comitê de TIC ou instância colegiada equivalente.
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova atuação efetiva do Comitê de TIC ou instância equivalente.
 Contexto da situação encontrada: S1.6 - Comitê de TIC ou instância equivalente formalmente instituído, mas sem evidência de atuação efetiva.
-Item de evidência avaliado: q1001evi.
 Evidência esperada no questionário: regimento do comitê de TI e atas que comprovem sua atuação, registros de reuniões, deliberações, pautas, encaminhamentos, registros de acompanhamento ou documentos equivalentes.
-Critérios da matriz aplicáveis: C4 - COBIT 2019 EDM01.02; C6 - COBIT 2019 MEA01.04; C7 - Decreto nº 9.203/2017, art. 6º; C8 - Decreto nº 12.198/2024, art. 5º; C10 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.1.
 Checklist obrigatório:
 1. Verifique se há evidência de reuniões realizadas pelo Comitê de TIC ou instância equivalente.
 2. Verifique se há atas, pautas, deliberações, encaminhamentos, listas de presença, decisões registradas ou documentos equivalentes.
@@ -900,110 +870,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q1-S1.6-q1001evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="130" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_avaliacao</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>questao_auditoria</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>situacao_encontrada</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>item_evidencia</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>descricao_avaliacao</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>prompt_checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.1-q2101evi</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>S2.1 - Inexistência ou fragilidade do processo formal de planejamento de TIC.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>q2101evi</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova processo formal de planejamento de TIC com participação, priorização e análise de benefícios, custos e riscos.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.1-q2101evi.
-Objetivo da avaliação: verificar se a evidência comprova processo formal de planejamento de TIC, com participação das áreas demandantes, critérios de priorização e análise de benefícios, custos e riscos.
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova processo formal de planejamento de TIC com participação, priorização e análise de benefícios, custos e riscos.
 Contexto da situação encontrada: S2.1 - Inexistência ou fragilidade do processo formal de planejamento de TIC.
-Item de evidência avaliado: q2101evi.
 Evidência esperada no questionário: norma ou procedimento formal que discipline o planejamento; plano de TI vigente; registros de participação das áreas demandantes; critérios de priorização documentados; estudos de custo, benefício e risco; atas de reuniões de planejamento; evidências de integração com planejamento institucional; relatórios de avaliação e revisão do processo; ou outras evidências cabíveis.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO02.05; C3 - COBIT 2019 APO05.03; C5 - COBIT 2019 APO06.02; C6 - COBIT 2019 APO06.03; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento disciplina processo de planejamento de TIC, com etapas, responsáveis ou orientações para sua execução.
@@ -1017,55 +928,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.1-q2101evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="210" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.2-q2102evi</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>S2.2 - Inexistência, desatualização, ausência de vigência ou ausência de aprovação formal do plano de TIC.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>q2102evi</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova plano de TIC existente, vigente e formalmente aprovado.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.2-q2102evi.
-Objetivo da avaliação: verificar se a evidência comprova plano de TIC existente, vigente e formalmente aprovado por instância competente.
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova plano de TIC existente, vigente e formalmente aprovado.
 Contexto da situação encontrada: S2.2 - Inexistência, desatualização, ausência de vigência ou ausência de aprovação formal do plano de TIC.
-Item de evidência avaliado: q2102evi.
 Evidência esperada no questionário: documento de plano de TI vigente aprovado pela alta administração; publicação do plano, se aplicável; vinculação com orçamento e plano de contratações; alinhamento com planejamento institucional; relatórios ou atas de acompanhamento da execução; indicadores e revisões do plano; ou outras evidências cabíveis.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO02.05; C2 - COBIT 2019 APO02.06; C5 - COBIT 2019 APO06.02; C6 - COBIT 2019 APO06.03; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Identifique se a evidência contém plano de TIC, PDTI, PEDTIC, PEI de TI ou instrumento equivalente.
 2. Verifique se o plano se refere à organização auditada e possui abrangência compatível com suas unidades ou áreas relevantes.
@@ -1078,55 +985,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.2-q2102evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="210" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.3-q2102evi</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>S2.3 - Plano de TIC sem conteúdo mínimo suficiente para orientar a gestão.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>q2102evi</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verificar se o plano de TIC contém objetivos, iniciativas, responsáveis, prazos, metas ou indicadores suficientes para orientar a gestão.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.3-q2102evi.
-Objetivo da avaliação: verificar se o plano de TIC contém conteúdo mínimo suficiente para orientar a gestão.
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se o plano de TIC contém objetivos, iniciativas, responsáveis, prazos, metas ou indicadores suficientes para orientar a gestão.
 Contexto da situação encontrada: S2.3 - Plano de TIC sem conteúdo mínimo suficiente para orientar a gestão.
-Item de evidência avaliado: q2102evi.
 Evidência esperada no questionário: documento de plano de TI vigente aprovado pela alta administração, com elementos que orientem investimentos, contratações e execução da TI, incluindo objetivos, iniciativas, responsáveis, prazos, metas ou indicadores.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO02.05; C2 - COBIT 2019 APO02.06; C3 - COBIT 2019 APO05.03; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Verifique se o plano apresenta objetivos de TIC ou objetivos estratégicos relacionados à TIC.
 2. Verifique se o plano apresenta iniciativas, projetos, ações ou aquisições de TIC.
@@ -1140,55 +1043,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.3-q2102evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="210" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.4-q2102evi</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>S2.4 - Plano de TIC sem alinhamento adequado ao planejamento institucional.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>q2102evi</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Verificar se o plano de TIC explicita alinhamento ao planejamento institucional ou a diretrizes superiores aplicáveis.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.4-q2102evi.
-Objetivo da avaliação: verificar se o plano de TIC está alinhado ao planejamento institucional e a diretrizes superiores aplicáveis.
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se o plano de TIC explicita alinhamento ao planejamento institucional ou a diretrizes superiores aplicáveis.
 Contexto da situação encontrada: S2.4 - Plano de TIC sem alinhamento adequado ao planejamento institucional.
-Item de evidência avaliado: q2102evi.
 Evidência esperada no questionário: plano de TI com alinhamento ao planejamento institucional, como PPA, plano estratégico, planos setoriais, plano de governo municipal ou diretrizes de instâncias superiores de governança, quando aplicável.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO02.05; C2 - COBIT 2019 APO02.06; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Verifique se o plano identifica instrumentos de planejamento institucional usados como referência.
 2. Verifique se objetivos, iniciativas, projetos ou ações de TIC são vinculados a objetivos institucionais, programas, metas, diretrizes superiores ou necessidades das áreas finalísticas e administrativas.
@@ -1201,55 +1100,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.4-q2102evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="210" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.5-q2102evi</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>S2.5 - Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>q2102evi</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Verificar se o plano de TIC demonstra integração com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.5-q2102evi.
-Objetivo da avaliação: verificar se o plano de TIC demonstra integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se o plano de TIC demonstra integração com orçamento, plano de contratações, projetos ou contratações de TIC.
 Contexto da situação encontrada: S2.5 - Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.
-Item de evidência avaliado: q2102evi.
 Evidência esperada no questionário: plano de TI com vinculação com orçamento e plano de contratações; identificação de iniciativas, projetos, investimentos, contratações ou aquisições; priorização de demandas; ou outras evidências cabíveis de integração entre planejamento de TIC, orçamento e contratações.
-Critérios da matriz aplicáveis: C3 - COBIT 2019 APO05.03; C4 - COBIT 2019 APO05.04; C5 - COBIT 2019 APO06.02; C6 - COBIT 2019 APO06.03; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Verifique se o plano de TIC identifica iniciativas, projetos, ações, investimentos, aquisições ou contratações de TIC.
 2. Verifique se há vínculo entre o plano de TIC e a proposta orçamentária, dotação, estimativa de recursos, fonte de financiamento ou priorização orçamentária.
@@ -1262,55 +1157,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.5-q2102evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="210" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.5-q2802evi</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>S2.5 - Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>q2802evi</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verificar se o planejamento anual das contratações demonstra integração com planejamento institucional, orçamento e demandas de TIC.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.5-q2802evi.
-Objetivo da avaliação: verificar se o planejamento anual das contratações demonstra integração com planejamento institucional, orçamento e demandas ou contratações de TIC.
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se o planejamento anual das contratações demonstra integração com planejamento institucional, orçamento e demandas de TIC.
 Contexto da situação encontrada: S2.5 - Plano de TIC sem integração adequada com orçamento, plano de contratações, projetos ou contratações de TIC.
-Item de evidência avaliado: q2802evi.
 Evidência esperada no questionário: Plano de Contratações Anual (PCA); normativos ou procedimentos relacionados; registros de participação das áreas envolvidas; aprovação pela alta administração; integração com planejamento institucional e orçamento; publicação no PNCP; cronogramas; ou outras evidências cabíveis.
-Critérios da matriz aplicáveis: C3 - COBIT 2019 APO05.03; C4 - COBIT 2019 APO05.04; C5 - COBIT 2019 APO06.02; C6 - COBIT 2019 APO06.03; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6 e subitens 9.1.6.1 a 9.1.6.4; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Identifique se a evidência contém PCA, procedimento de planejamento anual das contratações, cronograma, ata, aprovação ou instrumento equivalente.
 2. Verifique se o PCA ou instrumento equivalente considera instrumentos de planejamento da organização.
@@ -1324,55 +1215,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.5-q2802evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="210" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Q2-S2.6-q2102evi</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Q2 - Planejamento de TIC</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>S2.6 - Ausência de acompanhamento, revisão ou atualização periódica do plano de TIC.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>q2102evi</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Verificar se há registros de acompanhamento, revisão ou atualização periódica do plano de TIC.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q2-S2.6-q2102evi.
-Objetivo da avaliação: verificar se a evidência comprova acompanhamento, revisão ou atualização periódica do plano de TIC.
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se há registros de acompanhamento, revisão ou atualização periódica do plano de TIC.
 Contexto da situação encontrada: S2.6 - Ausência de acompanhamento, revisão ou atualização periódica do plano de TIC.
-Item de evidência avaliado: q2102evi.
 Evidência esperada no questionário: relatórios ou atas de acompanhamento da execução; indicadores e revisões do plano; registros de execução, pendências, reprogramações, deliberações, ajustes ou outras evidências cabíveis de acompanhamento do plano de TI.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO02.05; C2 - COBIT 2019 APO02.06; C3 - COBIT 2019 APO05.03; C7 - Acórdão 1.411/2014-TCU-Plenário, item 9.1.6; C8 - Acórdão TCE-RJ 44.490/2024-PLEN, item II.3.
 Checklist obrigatório:
 1. Verifique se há relatórios, atas, painéis, registros de execução ou documentos equivalentes de acompanhamento do plano de TIC.
 2. Verifique se há indicadores, metas, status de iniciativas, execução de ações, pendências ou resultados acompanhados.
@@ -1385,110 +1272,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q2-S2.6-q2102evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F8"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="78" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="56" customWidth="1" min="5" max="5"/>
-    <col width="130" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_avaliacao</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>questao_auditoria</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>situacao_encontrada</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>item_evidencia</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>descricao_avaliacao</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>prompt_checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="210" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.2-q2703evi</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>S3.2 - A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>q2703evi</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova definição documentada do quantitativo necessário de pessoal de TIC/SI com base em critérios ou procedimentos técnicos.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.2-q2703evi.
-Objetivo da avaliação: verificar se a evidência comprova definição documentada do quantitativo necessário de pessoal de TIC e segurança da informação com base em critérios ou procedimentos técnicos.
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova definição documentada do quantitativo necessário de pessoal de TIC/SI com base em critérios ou procedimentos técnicos.
 Contexto da situação encontrada: S3.2 - A organização não definiu o quantitativo necessário de pessoal de TIC e segurança da informação.
-Item de evidência avaliado: q2703evi.
 Evidência esperada no questionário: política ou metodologia de dimensionamento; estudos ou relatórios técnicos; definição documentada do quantitativo necessário; critérios utilizados, como serviços, sistemas, demanda, riscos ou complexidade; revisões periódicas; planos de provimento; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C2 - COBIT 2019 APO07.01; C5 - COBIT 2019 APO07.05; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
 2. Verifique se a evidência se refere à organização auditada e ao período ou contexto avaliado.
@@ -1501,56 +1329,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.2-q2703evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="210" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.4-q2701evi</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>q2701evi</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova perfis profissionais definidos para gestores de TIC e segurança da informação.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.4-q2701evi.
-Objetivo da avaliação: verificar se a evidência comprova perfis profissionais definidos e documentados para gestores de TIC e segurança da informação.
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova perfis profissionais definidos para gestores de TIC e segurança da informação.
 Contexto da situação encontrada: S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.
-Item de evidência avaliado: q2701evi.
 Evidência esperada no questionário: normativos ou documentos com atribuições e competências; descrições de cargos ou funções; matrizes de competências; registros de revisão periódica; publicações em portal institucional ou transparência ativa; atos de designação; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento define responsabilidades e atribuições de gestores de TIC ou segurança da informação.
@@ -1563,56 +1386,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.4-q2701evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="210" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.4-q2702evi</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>q2702evi</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova perfis profissionais definidos para colaboradores de TIC e segurança da informação.</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.4-q2702evi.
-Objetivo da avaliação: verificar se a evidência comprova perfis profissionais definidos e documentados para colaboradores de TIC e segurança da informação.
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova perfis profissionais definidos para colaboradores de TIC e segurança da informação.
 Contexto da situação encontrada: S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.
-Item de evidência avaliado: q2702evi.
 Evidência esperada no questionário: descrições de cargos ou funções; matrizes de competências; normativos com atribuições e responsabilidades; registros de revisão periódica; publicações em portal institucional ou mecanismos de transparência; planos de capacitação relacionados; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controles 5.2 e 6.3.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o documento define responsabilidades e atribuições de colaboradores, ocupações ou grupos de ocupações de TIC/SI.
@@ -1625,56 +1443,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.4-q2702evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="210" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.4-q2704evi</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>q2704evi</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova que a escolha de gestores de TIC/SI utiliza perfis profissionais previamente definidos.</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.4-q2704evi.
-Objetivo da avaliação: verificar se a evidência comprova que a escolha de gestores de TIC e segurança da informação ocorre segundo perfis profissionais previamente definidos e documentados.
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova que a escolha de gestores de TIC/SI utiliza perfis profissionais previamente definidos.
 Contexto da situação encontrada: S3.4 - Perfis profissionais de TIC e segurança da informação inexistentes, insuficientes ou não utilizados na escolha de gestores.
-Item de evidência avaliado: q2704evi.
 Evidência esperada no questionário: perfis profissionais documentados; critérios de seleção; registros de avaliação prévia de impedimentos legais; utilização de entrevistas, análises curriculares ou outras ferramentas estruturadas; currículos publicados; atos de designação; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C2 - COBIT 2019 APO07.01; C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusulas 5.3 e 7.2.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se há perfis profissionais previamente definidos para os cargos ou funções de gestão avaliados.
@@ -1687,56 +1500,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.4-q2704evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="210" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.5-q2705evi</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>q2705evi</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova identificação documentada de lacunas de competências de gestores, colaboradores de TIC e segurança da informação.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.5-q2705evi.
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
 Objetivo da avaliação: verificar se a evidência comprova identificação documentada de lacunas de competências de gestores, colaboradores de TIC e segurança da informação.
 Contexto da situação encontrada: S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.
-Item de evidência avaliado: q2705evi.
 Evidência esperada no questionário: matrizes de competências; avaliações de perfil; levantamentos de necessidades de capacitação; diagnósticos de competências técnicas e gerenciais; planos de desenvolvimento; relatórios ou registros documentados; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusula 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controle 6.3.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
 2. Verifique se a evidência identifica lacunas de competências de liderança, gestão, TIC ou segurança da informação.
@@ -1749,56 +1557,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.5-q2705evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="210" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.5-q2706evi</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>q2706evi</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova tratamento das lacunas de competências em TIC e segurança da informação.</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.5-q2706evi.
-Objetivo da avaliação: verificar se a evidência comprova tratamento das lacunas de competências dos colaboradores e gestores de TIC e segurança da informação.
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova tratamento das lacunas de competências em TIC e segurança da informação.
 Contexto da situação encontrada: S3.5 - Lacunas de competências dos colaboradores e gestores de TIC e segurança da informação não são identificadas ou tratadas.
-Item de evidência avaliado: q2706evi.
 Evidência esperada no questionário: plano de capacitação ou treinamento; registros de participação em cursos e treinamentos; ações de incentivo à capacitação; acompanhamento de participação e resultados; revisões periódicas do plano de capacitação; contratações ou apoio especializado; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C4 - COBIT 2019 APO07.03; C9 - ABNT NBR ISO/IEC 27001:2022, cláusula 7.2; C10 - ABNT NBR ISO/IEC 27002:2022, controle 6.3.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
 2. Verifique se a evidência apresenta plano, ações ou mecanismos de tratamento de lacunas de competências em TIC/SI.
@@ -1811,56 +1614,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.5-q2706evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="210" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.6-q2703evi</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>q2703evi</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência de dimensionamento de pessoal demonstra capacidade interna mínima para coordenar e fiscalizar TIC em modelo terceirizado ou externo.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.6-q2703evi.
-Objetivo da avaliação: verificar se a evidência de dimensionamento de pessoal demonstra capacidade interna mínima para coordenação, planejamento, aprovação técnica e fiscalização de TIC quando houver dependência relevante de terceiros ou estrutura externa.
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência de dimensionamento de pessoal demonstra capacidade interna mínima para coordenar e fiscalizar TIC em modelo terceirizado ou externo.
 Contexto da situação encontrada: S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.
-Item de evidência avaliado: q2703evi.
 Evidência esperada no questionário: política ou metodologia de dimensionamento; estudos ou relatórios técnicos; definição documentada do quantitativo necessário; critérios utilizados, como serviços, sistemas, demanda, riscos ou complexidade; revisões periódicas; planos de provimento; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C2 - COBIT 2019 APO07.01; C5 - COBIT 2019 APO07.05; C6 - COBIT 2019 APO07.06; C8 - COBIT 2019 DSS01.02.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal, técnico ou institucional.
 2. Verifique se a evidência considera a dependência de terceiros, estrutura externa, contratos ou serviços críticos de TIC no dimensionamento de pessoal.
@@ -1873,56 +1671,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.6-q2703evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="210" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.6-q2801evi</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>q2801evi</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova processo e artefatos de gestão e fiscalização contratual de TIC com papéis, responsabilidades e controles suficientes.</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.6-q2801evi.
-Objetivo da avaliação: verificar se a evidência comprova processo e artefatos de gestão e fiscalização contratual de TIC capazes de assegurar coordenação, fiscalização e responsabilização interna sobre terceiros.
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova processo e artefatos de gestão e fiscalização contratual de TIC com papéis, responsabilidades e controles suficientes.
 Contexto da situação encontrada: S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.
-Item de evidência avaliado: q2801evi.
 Evidência esperada no questionário: manuais, fluxos, normas ou procedimentos internos; modelos padronizados de documentos; checklists; definição de papéis e responsabilidades; fluxogramas; instruções de trabalho; artefatos de planejamento da contratação; processos de fiscalização contratual; referências à Lei 14.133/2021 e normativos correlatos; ou outras evidências cabíveis, indicando a abrangência na organização.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C6 - COBIT 2019 APO07.06; C7 - COBIT 2019 APO10.04; C8 - COBIT 2019 DSS01.02.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se o processo de gestão e fiscalização de contratos de TIC define etapas, responsáveis, papéis e controles.
@@ -1935,56 +1728,51 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.6-q2801evi",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="210" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Q3-S3.6-q2804eviA</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Q3 - Capacidade Institucional de TIC e Segurança da Informação</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>q2804eviA</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Verificar se a evidência comprova aprovação técnica da área de TIC em norma regulamentadora e em caso concreto de contratação.</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você é avaliador de evidências da Fiscalização TCE-RJ nº 18/2026 - iGovTI 2026. Analise exclusivamente a evidência anexada ao item indicado. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência fornecida.
-ID da avaliação: Q3-S3.6-q2804eviA.
-Objetivo da avaliação: verificar se a evidência comprova que contratações de soluções de TIC são submetidas à análise prévia e aprovação técnica da área de gestão de TIC, com norma regulamentadora e caso concreto.
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova aprovação técnica da área de TIC em norma regulamentadora e em caso concreto de contratação.
 Contexto da situação encontrada: S3.6 - Modelo de operação de TIC predominantemente terceirizado ou externo, sem capacidade interna mínima declarada para coordenação, planejamento, aprovação técnica ou fiscalização das atividades críticas de TIC.
-Item de evidência avaliado: q2804eviA.
 Evidência esperada no questionário: norma regulamentando o processo de análise prévia e aprovação técnica da área de gestão de TIC e evidência de um caso concreto de contratação em que essa aprovação tenha ocorrido.
-Critérios da matriz aplicáveis: C1 - COBIT 2019 APO01.05; C6 - COBIT 2019 APO07.06; C7 - COBIT 2019 APO10.04; C8 - COBIT 2019 DSS01.02.
 Checklist obrigatório:
 1. Identifique o tipo documental apresentado e se ele possui caráter formal ou institucional.
 2. Verifique se há norma, fluxo, procedimento ou instrumento equivalente que exija análise prévia e aprovação técnica pela área de TIC.
@@ -1997,393 +1785,803 @@
 Contrato de saída obrigatório:
 Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
 {
-  "id_avaliacao": "Q3-S3.6-q2804eviA",
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.
-</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F10"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
-    <col width="120" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_avaliacao</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>questao_auditoria</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>situacao_encontrada</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>item_evidencia</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>descricao_avaliacao</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>prompt_checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="110" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.1-q2201evi</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>S4.1 - Inexist?ncia, desatualiza??o, indisponibilidade ou insufici?ncia do cat?logo de servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>S4.1 - Inexist?ncia, desatualização, indisponibilidade ou insuficiência do catálogo de serviços de TIC</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>q2201evi</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova cat?logo de servi?os de TIC vigente, atualizado, acess?vel e aderente aos servi?os efetivamente prestados.</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2201evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.1 - Inexist?ncia, desatualiza??o, indisponibilidade ou insufici?ncia do cat?logo de servi?os de TIC.
-Item de evid?ncia: q2201evi.
-Evid?ncia esperada no question?rio: evid?ncia do cat?logo e da gest?o de n?veis de servi?o, como cat?logo de servi?os vigente, ANS firmados, defini??o de metas, registros de monitoramento, relat?rios de desempenho, canais de atendimento definidos ou evid?ncias equivalentes, indicando a abrang?ncia na organiza??o.
-Crit?rios aplic?veis da matriz: C1 - ITIL 4, gerenciamento do cat?logo de servi?os; C2 - COBIT 2019, APO09.02, catalogar servi?os facilitados por TI.
-Checklist objetivo:
-1. Verificar se h? cat?logo de servi?os de TIC em documento, portal, sistema ou instrumento equivalente.
-2. Verificar se o cat?logo identifica servi?os efetivamente prestados pela ?rea de TIC e n?o apenas uma lista gen?rica de atividades.
-3. Verificar se o cat?logo cont?m informa??es m?nimas para solicita??o ou uso dos servi?os, como descri??o, p?blico-alvo, canal de atendimento, ponto de contato, prazo, hor?rio de suporte ou meta aplic?vel.
-4. Verificar se h? indica??o de atualiza??o, vig?ncia ou compatibilidade com os servi?os e acordos de n?vel de servi?o declarados.
-5. Verificar se a evid?ncia demonstra disponibilidade ou acessibilidade do cat?logo aos usu?rios, ?reas demandantes ou equipes de suporte.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.1-q2201evi".</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="110" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova catálogo de serviços de TIC vigente, atualizado, acess?vel e aderente aos serviços efetivamente prestados.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova catálogo de serviços de TIC vigente, atualizado, acess?vel e aderente aos serviços efetivamente prestados.
+Contexto da situação encontrada: S4.1 - Inexist?ncia, desatualização, indisponibilidade ou insuficiência do catálogo de serviços de TIC
+Evidência esperada no questionário: evidência do catálogo e da gest?o de níveis de servi?o, como catálogo de serviços vigente, ANS firmados, defini??o de metas, registros de monitoramento, relat?rios de desempenho, canais de atendimento definidos ou evidências equivalentes, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verificar se h? catálogo de serviços de TIC em documento, portal, sistema ou instrumento equivalente.
+2. Verificar se o catálogo identifica serviços efetivamente prestados pela área de TIC e n?o apenas uma lista gen?rica de atividades.
+3. Verificar se o catálogo cont?m informações mínimas para solicita??o ou uso dos serviços, como descri??o, público-alvo, canal de atendimento, ponto de contato, prazo, horário de suporte ou meta aplic?vel.
+4. Verificar se h? indica??o de atualização, vigência ou compatibilidade com os serviços e acordos de n?vel de servi?o declarados.
+5. Verificar se a evidência demonstra disponibilidade ou acessibilidade do catálogo aos usuários, áreas demandantes ou equipes de suporte.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.2-q2201evi</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>S4.2 - Inexist?ncia de ANS, metas m?nimas ou monitoramento de n?veis de servi?o para os principais servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>S4.2 - Inexist?ncia de ANS, metas mínimas ou monitoramento de níveis de servi?o para os principais serviços de TIC</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>q2201evi</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova ANS, metas m?nimas e monitoramento de n?veis de servi?o para os principais servi?os de TIC.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2201evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.2 - Inexist?ncia de ANS, metas m?nimas ou monitoramento de n?veis de servi?o para os principais servi?os de TIC.
-Item de evid?ncia: q2201evi.
-Evid?ncia esperada no question?rio: evid?ncia do cat?logo e da gest?o de n?veis de servi?o, como cat?logo de servi?os vigente, ANS firmados, defini??o de metas, registros de monitoramento, relat?rios de desempenho, canais de atendimento definidos ou evid?ncias equivalentes, indicando a abrang?ncia na organiza??o.
-Crit?rios aplic?veis da matriz: C2 - COBIT 2019, APO09.02, catalogar servi?os facilitados por TI; C3 - ITIL 4, gerenciamento de n?vel de servi?o.
-Checklist objetivo:
-1. Verificar se h? ANS, metas m?nimas, indicadores ou par?metros objetivos de atendimento para servi?os de TIC relevantes.
-2. Verificar se os n?veis de servi?o ou metas est?o associados a servi?os identific?veis e a ?reas usu?rias ou clientes internos.
-3. Verificar se h? registros de monitoramento peri?dico, relat?rios, pain?is, atas ou evid?ncias equivalentes sobre cumprimento dos n?veis de servi?o.
-4. Verificar se a evid?ncia permite identificar resultados, desvios, descumprimentos ou medidas de acompanhamento.
-5. Verificar se a evid?ncia ? compat?vel com a resposta declarat?ria e demonstra abrang?ncia suficiente na organiza??o.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.2-q2201evi".</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="110" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova ANS, metas mínimas e monitoramento de níveis de servi?o para os principais serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova ANS, metas mínimas e monitoramento de níveis de servi?o para os principais serviços de TIC.
+Contexto da situação encontrada: S4.2 - Inexist?ncia de ANS, metas mínimas ou monitoramento de níveis de servi?o para os principais serviços de TIC
+Evidência esperada no questionário: evidência do catálogo e da gest?o de níveis de servi?o, como catálogo de serviços vigente, ANS firmados, defini??o de metas, registros de monitoramento, relat?rios de desempenho, canais de atendimento definidos ou evidências equivalentes, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verificar se h? ANS, metas mínimas, indicadores ou parâmetros objetivos de atendimento para serviços de TIC relevantes.
+2. Verificar se os níveis de servi?o ou metas est?o associados a serviços identific?veis e a áreas usu?rias ou clientes internos.
+3. Verificar se h? registros de monitoramento periódico, relat?rios, painéis, atas ou evidências equivalentes sobre cumprimento dos níveis de servi?o.
+4. Verificar se a evidência permite identificar resultados, desvios, descumprimentos ou medidas de acompanhamento.
+5. Verificar se a evidência ? compat?vel com a resposta declaratória e demonstra abrangência suficiente na organização.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.3-q2203evi</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>q2203evi</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova invent?rio atualizado de ativos e servi?os de TI no contexto da gest?o de configura??o e ativos.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2203evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC.
-Item de evid?ncia: q2203evi.
-Evid?ncia esperada no question?rio: evid?ncia da gest?o de configura??o e ativos, como invent?rio atualizado de ativos e servi?os de TI, CMDB ou base equivalente, relacionamentos entre sistemas, infraestrutura e servi?os, uso dessas informa??es em mudan?as, norma ou procedimento formal, relat?rios ou ferramentas de controle.
-Crit?rios aplic?veis da matriz: C4 - ITIL 4, gerenciamento de ativos de TI; C5 - ITIL 4, gerenciamento de configura??o de servi?o.
-Checklist objetivo:
-1. Verificar se h? invent?rio ou base consolidada de ativos de TIC, servi?os de TI ou itens de configura??o relevantes.
-2. Verificar se o invent?rio cont?m elementos m?nimos como identifica??o do ativo, tipo, servi?o relacionado, respons?vel, localiza??o, ambiente, sistema, software, equipamento ou componente de infraestrutura.
-3. Verificar se a evid?ncia indica atualiza??o, manuten??o peri?dica ou uso operacional da base.
-4. Verificar se a evid?ncia demonstra relacionamento entre ativos, sistemas, infraestrutura e servi?os, quando aplic?vel.
-5. Verificar se a abrang?ncia ? suficiente para os principais servi?os ou ativos de TIC da organiza??o.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.3-q2203evi".</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="110" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova invent?rio atualizado de ativos e serviços de TI no contexto da gest?o de configura??o e ativos.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova invent?rio atualizado de ativos e serviços de TI no contexto da gest?o de configura??o e ativos.
+Contexto da situação encontrada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC
+Evidência esperada no questionário: evidência da gest?o de configura??o e ativos, como invent?rio atualizado de ativos e serviços de TI, CMDB ou base equivalente, relacionamentos entre sistemas, infraestrutura e serviços, uso dessas informações em mudan?as, norma ou procedimento formal, relat?rios ou ferramentas de controle.
+Checklist obrigatório:
+1. Verificar se h? invent?rio ou base consolidada de ativos de TIC, serviços de TI ou itens de configura??o relevantes.
+2. Verificar se o invent?rio cont?m elementos m?nimos como identificação do ativo, tipo, servi?o relacionado, respons?vel, localização, ambiente, sistema, software, equipamento ou componente de infraestrutura.
+3. Verificar se a evidência indica atualização, manuten??o periódica ou uso operacional da base.
+4. Verificar se a evidência demonstra relacionamento entre ativos, sistemas, infraestrutura e serviços, quando aplic?vel.
+5. Verificar se a abrangência ? suficiente para os principais serviços ou ativos de TIC da organização.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.3-q2501evi</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>q2501evi</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova invent?rio de ativos associados ? informa??o e defini??o de respons?veis por ativos relevantes.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2501evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC.
-Item de evid?ncia: q2501evi.
-Evid?ncia esperada no question?rio: evid?ncia da gest?o de ativos associados ? informa??o, como invent?rio de ativos e informa??es cr?ticas, defini??o formal de respons?veis, identifica??o de informa??es cr?ticas, controles de prote??o, norma ou procedimento formal e relat?rios de acompanhamento.
-Crit?rios aplic?veis da matriz: C4 - ITIL 4, gerenciamento de ativos de TI.
-Checklist objetivo:
-1. Verificar se h? invent?rio de ativos associados ? informa??o, tais como sistemas, bases de dados, documentos digitais, backups, equipamentos ou outros ativos que armazenem, processem ou transmitam informa??es.
-2. Verificar se o invent?rio identifica ativos ou informa??es cr?ticas, sens?veis ou relevantes para os servi?os da organiza??o.
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova invent?rio de ativos associados ? informa??o e defini??o de respons?veis por ativos relevantes.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova invent?rio de ativos associados ? informa??o e defini??o de respons?veis por ativos relevantes.
+Contexto da situação encontrada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC
+Evidência esperada no questionário: evidência da gest?o de ativos associados ? informa??o, como invent?rio de ativos e informações cr?ticas, defini??o formal de respons?veis, identificação de informações cr?ticas, controles de prote??o, norma ou procedimento formal e relat?rios de acompanhamento.
+Checklist obrigatório:
+1. Verificar se h? invent?rio de ativos associados ? informa??o, tais como sistemas, bases de dados, documentos digitais, backups, equipamentos ou outros ativos que armazenem, processem ou transmitam informações.
+2. Verificar se o invent?rio identifica ativos ou informações cr?ticas, sens?veis ou relevantes para os serviços da organização.
 3. Verificar se h? respons?veis formalmente definidos pelos ativos ou pelo processo de gest?o dos ativos.
-4. Verificar se a evid?ncia indica atualiza??o, revis?o ou acompanhamento do invent?rio.
-5. Verificar se a evid?ncia ? documental e suficiente, e n?o apenas declara??o gen?rica de que o processo existe.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.3-q2501evi".</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="110" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+4. Verificar se a evidência indica atualização, revis?o ou acompanhamento do invent?rio.
+5. Verificar se a evidência ? documental e suficiente, e n?o apenas declara??o gen?rica de que o processo existe.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.3-q2504evi</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>q2504evi</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova invent?rio e controle de dispositivos e softwares conectados ? rede ou usados nos servi?os de TIC.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2504evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC.
-Item de evid?ncia: q2504evi.
-Evid?ncia esperada no question?rio: evid?ncia da gest?o da seguran?a dos recursos de processamento da informa??o, incluindo invent?rio de dispositivos e softwares, registros de controle, relat?rios, ferramentas ou outros documentos que demonstrem abrang?ncia na organiza??o.
-Crit?rios aplic?veis da matriz: C4 - ITIL 4, gerenciamento de ativos de TI.
-Checklist objetivo:
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova invent?rio e controle de dispositivos e softwares conectados ? rede ou usados nos serviços de TIC.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova invent?rio e controle de dispositivos e softwares conectados ? rede ou usados nos serviços de TIC.
+Contexto da situação encontrada: S4.3 - Inexist?ncia ou fragilidade do invent?rio de ativos de TIC
+Evidência esperada no questionário: evidência da gest?o da seguran?a dos recursos de processamento da informa??o, incluindo invent?rio de dispositivos e softwares, registros de controle, relat?rios, ferramentas ou outros documentos que demonstrem abrangência na organização.
+Checklist obrigatório:
 1. Verificar se h? invent?rio ou controle de dispositivos conectados ? rede, equipamentos, servidores, esta??es, recursos de nuvem ou componentes equivalentes.
 2. Verificar se h? invent?rio ou controle de softwares instalados, aplica??es, licen?as ou sistemas relevantes.
-3. Verificar se a evid?ncia cont?m dados suficientes para identifica??o, controle e atualiza??o dos ativos.
-4. Verificar se a evid?ncia demonstra abrang?ncia compat?vel com os principais ambientes ou servi?os de TIC.
-5. Desconsiderar controles de seguran?a n?o relacionados ao invent?rio quando eles n?o comprovarem identifica??o e controle de ativos.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.3-q2504evi".</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+3. Verificar se a evidência cont?m dados suficientes para identificação, controle e atualização dos ativos.
+4. Verificar se a evidência demonstra abrangência compat?vel com os principais ambientes ou serviços de TIC.
+5. Desconsiderar controles de seguran?a n?o relacionados ao invent?rio quando eles n?o comprovarem identificação e controle de ativos.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.4-q2203evi</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>S4.4 - Aus?ncia ou fragilidade do processo de gest?o de configura??o</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>q2203evi</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova processo formal ou mecanismo equivalente de gest?o de configura??o e seus relacionamentos.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2203evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.4 - Aus?ncia ou fragilidade do processo de gest?o de configura??o.
-Item de evid?ncia: q2203evi.
-Evid?ncia esperada no question?rio: evid?ncia da gest?o de configura??o e ativos, como invent?rio atualizado de ativos e servi?os de TI, CMDB ou base equivalente, relacionamentos entre sistemas, infraestrutura e servi?os, uso dessas informa??es em mudan?as, norma ou procedimento formal, relat?rios ou ferramentas de controle.
-Crit?rios aplic?veis da matriz: C5 - ITIL 4, gerenciamento de configura??o de servi?o; C6 - COBIT 2019, BAI10.01, estabelecer e manter modelo de configura??o.
-Checklist objetivo:
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova processo formal ou mecanismo equivalente de gest?o de configura??o e seus relacionamentos.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova processo formal ou mecanismo equivalente de gest?o de configura??o e seus relacionamentos.
+Contexto da situação encontrada: S4.4 - Aus?ncia ou fragilidade do processo de gest?o de configura??o
+Evidência esperada no questionário: evidência da gest?o de configura??o e ativos, como invent?rio atualizado de ativos e serviços de TI, CMDB ou base equivalente, relacionamentos entre sistemas, infraestrutura e serviços, uso dessas informações em mudan?as, norma ou procedimento formal, relat?rios ou ferramentas de controle.
+Checklist obrigatório:
 1. Verificar se h? norma, procedimento, guia, fluxo, pol?tica, ferramenta ou mecanismo equivalente para gest?o de configura??o.
-2. Verificar se a evid?ncia define ou demonstra itens de configura??o, atributos m?nimos, relacionamentos e respons?veis.
-3. Verificar se h? CMDB, base de configura??o, invent?rio estruturado ou ferramenta equivalente mantida pela organiza??o.
-4. Verificar se a base de configura??o ? usada ou referenciada em mudan?as, opera??o, an?lise de impacto ou gest?o dos servi?os.
-5. Verificar se a evid?ncia ? suficiente para comprovar processo executado ou mecanismo operacional, e n?o apenas inten??o futura.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.4-q2203evi".</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="110" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+2. Verificar se a evidência define ou demonstra itens de configura??o, atributos m?nimos, relacionamentos e respons?veis.
+3. Verificar se h? CMDB, base de configura??o, invent?rio estruturado ou ferramenta equivalente mantida pela organização.
+4. Verificar se a base de configura??o ? usada ou referenciada em mudan?as, opera??o, an?lise de impacto ou gest?o dos serviços.
+5. Verificar se a evidência ? suficiente para comprovar processo executado ou mecanismo operacional, e n?o apenas inten??o futura.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Q4-S4.5-q2204evi</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Q4 - Gest?o de Servi?os de TIC</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Q4 - Gestão de Serviços de TIC</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>S4.5 - Inexist?ncia ou fragilidade do processo de gest?o de incidentes de TIC</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>q2204evi</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evid?ncia comprova processo formal, registros rastre?veis e tratamento estruturado de incidentes de servi?os e de seguran?a da informa??o.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Voc? deve avaliar exclusivamente a evid?ncia anexada ao item q2204evi do question?rio iGovTI 2026, sem buscar informa??es externas e sem presumir fatos n?o comprovados.
-Quest?o de auditoria: Q4 - Gest?o de Servi?os de TIC.
-Situa??o encontrada avaliada: S4.5 - Inexist?ncia ou fragilidade do processo de gest?o de incidentes de TIC.
-Item de evid?ncia: q2204evi.
-Evid?ncia esperada no question?rio: evid?ncia da gest?o de incidentes, como norma ou procedimento formal, registros de incidentes, chamados ou tickets, crit?rios de prioriza??o e escalonamento, base de conhecimento, relat?rios de atendimento, tratamento de incidentes de seguran?a, an?lise de causa raiz e a??es corretivas.
-Crit?rios aplic?veis da matriz: C7 - ITIL 4, gerenciamento de incidentes; C8 - COBIT 2019, DSS02.02, DSS02.04 e DSS02.07, requisi??es de servi?o e incidentes gerenciados.
-Checklist objetivo:
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova processo formal, registros rastre?veis e tratamento estruturado de incidentes de serviços e de seguran?a da informa??o.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova processo formal, registros rastre?veis e tratamento estruturado de incidentes de serviços e de seguran?a da informa??o.
+Contexto da situação encontrada: S4.5 - Inexist?ncia ou fragilidade do processo de gest?o de incidentes de TIC
+Evidência esperada no questionário: evidência da gest?o de incidentes, como norma ou procedimento formal, registros de incidentes, chamados ou tickets, crit?rios de prioriza??o e escalonamento, base de conhecimento, relat?rios de atendimento, tratamento de incidentes de seguran?a, an?lise de causa raiz e a??es corretivas.
+Checklist obrigatório:
 1. Verificar se h? norma, procedimento, fluxo ou instrumento equivalente que formalize pap?is, responsabilidades, prioriza??o e escalamento de incidentes.
 2. Verificar se existem registros rastre?veis de incidentes, chamados, tickets, hist?rico de atendimento, respons?veis, datas, status e solu??o aplicada.
-3. Verificar se a resolu??o dos incidentes considera n?veis de servi?o, criticidade, impacto ou crit?rios objetivos de atendimento.
+3. Verificar se a resolu??o dos incidentes considera níveis de servi?o, criticidade, impacto ou crit?rios objetivos de atendimento.
 4. Verificar se h? tratamento de incidentes de seguran?a da informa??o, com notifica??o, resposta, comunica??o ou responsabilidades definidas.
-5. Verificar se h? an?lise posterior de incidentes relevantes ou recorrentes, causa raiz, base de conhecimento, a??es corretivas ou evid?ncias equivalentes.
-Retorne exclusivamente um JSON v?lido, sem coment?rios fora do JSON, com as chaves: "id_avaliacao", "resultado", "justificativa_sintetica", "elementos_comprovados", "lacunas" e "inconsistencias". O campo "resultado" deve ser exatamente "Conforme" ou "N?o conforme". Use "Conforme" somente quando a evid?ncia for existente, leg?vel, compat?vel, atualizada e suficiente para todos os elementos essenciais. Use "N?o conforme" quando a evid?ncia for inexistente, ileg?vel, incompat?vel, desatualizada, meramente declarat?ria sem comprova??o suficiente, ou quando faltar qualquer elemento essencial. N?o use classifica??es intermedi?rias como parcialmente conforme, parcialmente suficiente ou inconclusivo.
-O campo "id_avaliacao" deve ser "Q4-S4.5-q2204evi".</t>
+5. Verificar se h? an?lise posterior de incidentes relevantes ou recorrentes, causa raiz, base de conhecimento, a??es corretivas ou evidências equivalentes.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.1-q2801evi</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>S6.1 - Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>q2801evi</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova processo formal e padronizado para contratações de TIC, com fluxo, papéis, responsabilidades e artefatos mínimos.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova processo formal e padronizado para contratações de TIC, com fluxo, papéis, responsabilidades e artefatos mínimos.
+Contexto da situação encontrada: S6.1 - Inexistência ou fragilidade de processo formal e padronizado para contratações de TIC.
+Evidência esperada no questionário: manuais, fluxos, normas ou procedimentos internos; modelos padronizados de documentos; checklists; definição de papéis e responsabilidades; fluxogramas; instruções de trabalho; artefatos de planejamento da contratação; processos de fiscalização contratual; referências à Lei 14.133/2021 e normativos correlatos; ou outras evidências cabíveis, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verifique se a evidência possui caráter formal ou institucional, como norma, manual, fluxo, procedimento, guia, checklist ou instrumento equivalente.
+2. Verifique se a evidência contempla o planejamento da contratação de TIC, a seleção de fornecedores e a gestão ou fiscalização contratual.
+3. Verifique se há definição de etapas, responsáveis, papéis, instâncias ou artefatos resultantes para cada fase relevante.
+4. Verifique se a evidência inclui ou referencia modelos, checklists, minutas, instruções de trabalho ou artefatos padronizados aplicáveis às contratações de TIC.
+5. Verifique se a evidência indica aderência à Lei 14.133/2021 ou a normativos correlatos de contratação pública.
+6. Verifique se a abrangência é compatível com a organização auditada e não se limita a documento isolado, minuta informal ou prática não institucionalizada.
+7. Decida se a evidência comprova, de forma suficiente, processo formal e padronizado para contratações de TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.2-q2804eviA</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>S6.2 - Contratações de TIC sem análise prévia e aprovação técnica obrigatória da área de TIC.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>q2804eviA</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova norma de aprovação técnica obrigatória pela área de TIC e sua aplicação em caso concreto.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova norma de aprovação técnica obrigatória pela área de TIC e sua aplicação em caso concreto.
+Contexto da situação encontrada: S6.2 - Contratações de TIC sem análise prévia e aprovação técnica obrigatória da área de TIC.
+Evidência esperada no questionário: norma regulamentando o processo de submissão obrigatória das contratações de soluções de TI à análise prévia e aprovação técnica da área de gestão de TI, acompanhada de evidência de um caso concreto.
+Checklist obrigatório:
+1. Verifique se a evidência contém norma, procedimento, fluxo, despacho padrão ou instrumento equivalente que torne obrigatória a análise prévia da área de TIC.
+2. Verifique se a obrigação alcança contratações de soluções de TIC demandadas por áreas finalísticas, administrativas ou outras unidades da organização.
+3. Verifique se a evidência define momento, responsável, critérios ou forma de registro da aprovação técnica.
+4. Verifique se há caso concreto com manifestação, parecer, despacho, aprovação técnica ou registro equivalente da área de TIC.
+5. Verifique se o caso concreto se refere a contratação de TIC e é compatível com a organização auditada.
+6. Verifique se a evidência demonstra aprovação técnica anterior à contratação ou à decisão relevante de prosseguimento.
+7. Decida se a evidência comprova, de forma suficiente, análise prévia e aprovação técnica obrigatória da área de TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.3-q2102evi</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>S6.3 - Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>q2102evi</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se o plano de TIC evidencia vínculo com orçamento, plano de contratações, projetos ou contratações de TIC.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se o plano de TIC evidencia vínculo com orçamento, plano de contratações, projetos ou contratações de TIC.
+Contexto da situação encontrada: S6.3 - Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.
+Evidência esperada no questionário: documento vigente de plano de TI aprovado pela alta administração; publicação do plano, se aplicável; vinculação com orçamento e plano de contratações; alinhamento com planejamento institucional; relatórios ou atas de acompanhamento da execução; indicadores e revisões do plano; ou outras evidências cabíveis, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verifique se a evidência contém plano de TIC vigente ou instrumento equivalente aplicável à organização auditada.
+2. Verifique se o plano identifica iniciativas, projetos, ações ou necessidades de contratação de TIC.
+3. Verifique se há vínculo explícito ou rastreável entre o plano de TIC e orçamento, plano de contratações, projetos ou contratações executadas.
+4. Verifique se há priorização, programação, previsão de recursos ou indicação de responsáveis que permita orientar as contratações de TIC.
+5. Verifique se a evidência é compatível com a ideia de planejamento vigente, aprovado e aplicável ao período avaliado.
+6. Decida se a evidência comprova, de forma suficiente, integração entre planejamento de TIC e contratações.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.3-q2802evi</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>S6.3 - Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>q2802evi</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova planejamento anual das contratações integrado aos instrumentos de planejamento e ao orçamento.</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova planejamento anual das contratações integrado aos instrumentos de planejamento e ao orçamento.
+Contexto da situação encontrada: S6.3 - Contratações de TIC sem aderência ao plano de TIC, ao plano de contratações ou à proposta orçamentária.
+Evidência esperada no questionário: Plano de Contratações Anual (PCA); normativos ou procedimentos relacionados; registros de participação das áreas envolvidas; aprovação pela alta administração; integração com planejamento institucional e orçamento; publicação no PNCP; cronogramas; ou outras evidências cabíveis, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verifique se a evidência contém Plano de Contratações Anual, procedimento de planejamento anual das contratações ou instrumento equivalente.
+2. Verifique se a evidência se refere à organização auditada e ao período avaliado.
+3. Verifique se o planejamento anual considera instrumentos de planejamento da organização, especialmente plano de TIC quando houver contratações de TIC.
+4. Verifique se há vinculação com proposta orçamentária, previsão de recursos, cronograma ou priorização das contratações.
+5. Verifique se as contratações de TIC estão identificadas ou podem ser rastreadas no planejamento anual.
+6. Verifique se há aprovação, divulgação ou registro formal compatível com o PCA.
+7. Decida se a evidência comprova, de forma suficiente, aderência das contratações de TIC ao planejamento anual e ao orçamento.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.4-q2801evi</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>S6.4 - Contratações de TIC sem equipe de planejamento formalmente designada e com participação técnica de TIC.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>q2801evi</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova previsão formal de equipe de planejamento da contratação de TIC com participação técnica de TIC.</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova previsão formal de equipe de planejamento da contratação de TIC com participação técnica de TIC.
+Contexto da situação encontrada: S6.4 - Contratações de TIC sem equipe de planejamento formalmente designada e com participação técnica de TIC.
+Evidência esperada no questionário: manuais, fluxos, normas ou procedimentos internos; modelos padronizados de documentos; checklists; definição de papéis e responsabilidades; fluxogramas; instruções de trabalho; artefatos de planejamento da contratação; processos de fiscalização contratual; referências à Lei 14.133/2021 e normativos correlatos; ou outras evidências cabíveis, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verifique se a evidência define equipe, comissão, grupo ou responsáveis pela fase de planejamento das contratações de TIC.
+2. Verifique se há exigência de designação formal ou registro equivalente da equipe de planejamento.
+3. Verifique se a composição prevê, no mínimo, participação da área requisitante e de integrante técnico da área de TIC.
+4. Verifique se os papéis e responsabilidades dos integrantes da equipe são definidos de forma suficiente.
+5. Verifique se a previsão se aplica às contratações de TIC e não apenas a contratações genéricas sem participação técnica.
+6. Decida se a evidência comprova, de forma suficiente, previsão formal de equipe de planejamento com participação técnica de TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.5-q2801evi</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>S6.5 - Artefatos de planejamento das contratações de TIC sem requisitos técnicos, análise de riscos, segurança da informação, proteção de dados ou critérios objetivos de aceite.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>q2801evi</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova artefatos de planejamento com requisitos técnicos, riscos, segurança, proteção de dados e critérios objetivos de aceite.</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova artefatos de planejamento com requisitos técnicos, riscos, segurança, proteção de dados e critérios objetivos de aceite.
+Contexto da situação encontrada: S6.5 - Artefatos de planejamento das contratações de TIC sem requisitos técnicos, análise de riscos, segurança da informação, proteção de dados ou critérios objetivos de aceite.
+Evidência esperada no questionário: modelos padronizados de documentos, DFD, ETP, TR, Matriz de Riscos ou documentos equivalentes; manuais, fluxos, normas ou procedimentos internos; checklists; artefatos de planejamento da contratação; referências à Lei 14.133/2021 e normativos correlatos; ou outras evidências cabíveis, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verifique se a evidência contém ou referencia artefatos de planejamento de contratações de TIC, como DFD, ETP, TR, projeto básico, matriz de riscos ou checklist equivalente.
+2. Verifique se os artefatos ou modelos exigem definição de requisitos técnicos da solução de TIC.
+3. Verifique se há exigência de análise de riscos da contratação ou matriz de riscos aplicável.
+4. Verifique se há exigência de requisitos de segurança da informação e de proteção de dados pessoais quando a solução envolver tratamento de dados pessoais.
+5. Verifique se há critérios objetivos de aceite, recebimento, validação, homologação ou conformidade da solução contratada.
+6. Verifique se os artefatos são suficientemente aplicáveis às contratações de TIC e não apenas modelos genéricos sem conteúdo técnico mínimo.
+7. Decida se a evidência comprova, de forma suficiente, qualidade mínima dos artefatos de planejamento das contratações de TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Q6-S6.6-q2801evi</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Q6 - Contratações de TIC</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>S6.6 - Contratações de TIC sem níveis mínimos de serviço, métricas de desempenho ou critérios objetivos de fiscalização e recebimento.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>q2801evi</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Verificar se a evidência comprova previsão de NMS, métricas, critérios de fiscalização, recebimento e pagamento vinculado a resultados.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
+Objetivo da avaliação: verificar se a evidência comprova previsão de NMS, métricas, critérios de fiscalização, recebimento e pagamento vinculado a resultados.
+Contexto da situação encontrada: S6.6 - Contratações de TIC sem níveis mínimos de serviço, métricas de desempenho ou critérios objetivos de fiscalização e recebimento.
+Evidência esperada no questionário: processos de fiscalização contratual; modelos de plano de fiscalização, termos de recebimento, relatórios de acompanhamento, registros de ocorrências, avaliações de desempenho contratual, manuais, normas, procedimentos internos, checklists ou artefatos padronizados relativos à gestão e fiscalização de contratos de TI; ou outras evidências cabíveis, indicando a abrangência na organização.
+Checklist obrigatório:
+1. Verifique se a evidência prevê níveis mínimos de serviço, indicadores, métricas de desempenho ou parâmetros objetivos de qualidade para contratações de TIC.
+2. Verifique se há critérios de fiscalização, acompanhamento, registro de ocorrências, avaliação de desempenho ou gestão contratual.
+3. Verifique se há modelos ou orientações para recebimento provisório, recebimento definitivo, aceite, glosa ou rejeição do objeto.
+4. Verifique se a evidência vincula, quando aplicável, pagamento, aceite ou medição à efetiva entrega de resultados ou níveis de qualidade.
+5. Verifique se os critérios são objetivos e verificáveis, e não apenas afirmações genéricas de que o contrato será fiscalizado.
+6. Verifique se a evidência é aplicável às contratações de TIC e à organização auditada.
+7. Decida se a evidência comprova, de forma suficiente, controle objetivo de desempenho, fiscalização e recebimento nas contratações de TIC.
+Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
+Contrato de saída obrigatório:
+Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
+{
+  "resultado": "Conforme" ou "Não conforme",
+  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
+  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
+  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
+  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
+}
+Regra de decisão binária:
+- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
+- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
+- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F8"/>
+  <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/01-Planejamento/03-Estrategia_e_Plano/04-Matriz_Planejamento/matriz_verificaca_evidencias.xlsx
+++ b/01-Planejamento/03-Estrategia_e_Plano/04-Matriz_Planejamento/matriz_verificaca_evidencias.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2466,120 +2466,6 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Q6-S6.5-q2801evi</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Q6 - Contratações de TIC</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>S6.5 - Artefatos de planejamento das contratações de TIC sem requisitos técnicos, análise de riscos, segurança da informação, proteção de dados ou critérios objetivos de aceite.</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>q2801evi</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evidência comprova artefatos de planejamento com requisitos técnicos, riscos, segurança, proteção de dados e critérios objetivos de aceite.</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
-Objetivo da avaliação: verificar se a evidência comprova artefatos de planejamento com requisitos técnicos, riscos, segurança, proteção de dados e critérios objetivos de aceite.
-Contexto da situação encontrada: S6.5 - Artefatos de planejamento das contratações de TIC sem requisitos técnicos, análise de riscos, segurança da informação, proteção de dados ou critérios objetivos de aceite.
-Evidência esperada no questionário: modelos padronizados de documentos, DFD, ETP, TR, Matriz de Riscos ou documentos equivalentes; manuais, fluxos, normas ou procedimentos internos; checklists; artefatos de planejamento da contratação; referências à Lei 14.133/2021 e normativos correlatos; ou outras evidências cabíveis, indicando a abrangência na organização.
-Checklist obrigatório:
-1. Verifique se a evidência contém ou referencia artefatos de planejamento de contratações de TIC, como DFD, ETP, TR, projeto básico, matriz de riscos ou checklist equivalente.
-2. Verifique se os artefatos ou modelos exigem definição de requisitos técnicos da solução de TIC.
-3. Verifique se há exigência de análise de riscos da contratação ou matriz de riscos aplicável.
-4. Verifique se há exigência de requisitos de segurança da informação e de proteção de dados pessoais quando a solução envolver tratamento de dados pessoais.
-5. Verifique se há critérios objetivos de aceite, recebimento, validação, homologação ou conformidade da solução contratada.
-6. Verifique se os artefatos são suficientemente aplicáveis às contratações de TIC e não apenas modelos genéricos sem conteúdo técnico mínimo.
-7. Decida se a evidência comprova, de forma suficiente, qualidade mínima dos artefatos de planejamento das contratações de TIC.
-Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
-Contrato de saída obrigatório:
-Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
-{
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Q6-S6.6-q2801evi</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Q6 - Contratações de TIC</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>S6.6 - Contratações de TIC sem níveis mínimos de serviço, métricas de desempenho ou critérios objetivos de fiscalização e recebimento.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>q2801evi</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Verificar se a evidência comprova previsão de NMS, métricas, critérios de fiscalização, recebimento e pagamento vinculado a resultados.</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Você é avaliador de evidências de auditoria. Analise exclusivamente a evidência fornecida. Não busque informações externas, não presuma fatos não documentados e não utilize conhecimento fora da evidência analisada.
-Objetivo da avaliação: verificar se a evidência comprova previsão de NMS, métricas, critérios de fiscalização, recebimento e pagamento vinculado a resultados.
-Contexto da situação encontrada: S6.6 - Contratações de TIC sem níveis mínimos de serviço, métricas de desempenho ou critérios objetivos de fiscalização e recebimento.
-Evidência esperada no questionário: processos de fiscalização contratual; modelos de plano de fiscalização, termos de recebimento, relatórios de acompanhamento, registros de ocorrências, avaliações de desempenho contratual, manuais, normas, procedimentos internos, checklists ou artefatos padronizados relativos à gestão e fiscalização de contratos de TI; ou outras evidências cabíveis, indicando a abrangência na organização.
-Checklist obrigatório:
-1. Verifique se a evidência prevê níveis mínimos de serviço, indicadores, métricas de desempenho ou parâmetros objetivos de qualidade para contratações de TIC.
-2. Verifique se há critérios de fiscalização, acompanhamento, registro de ocorrências, avaliação de desempenho ou gestão contratual.
-3. Verifique se há modelos ou orientações para recebimento provisório, recebimento definitivo, aceite, glosa ou rejeição do objeto.
-4. Verifique se a evidência vincula, quando aplicável, pagamento, aceite ou medição à efetiva entrega de resultados ou níveis de qualidade.
-5. Verifique se os critérios são objetivos e verificáveis, e não apenas afirmações genéricas de que o contrato será fiscalizado.
-6. Verifique se a evidência é aplicável às contratações de TIC e à organização auditada.
-7. Decida se a evidência comprova, de forma suficiente, controle objetivo de desempenho, fiscalização e recebimento nas contratações de TIC.
-Ao aplicar o checklist, considere a evidência como um target binário para a regra de identificação da situação encontrada. O resultado "Não conforme" será usado pela matriz como indicativo de evidência inexistente, incompatível ou insuficiente para comprovar a prática avaliada.
-Contrato de saída obrigatório:
-Responda exclusivamente em JSON válido, sem texto fora do JSON, com os campos:
-{
-  "resultado": "Conforme" ou "Não conforme",
-  "justificativa_sintetica": "&lt;fundamento objetivo da decisão&gt;",
-  "elementos_comprovados": ["&lt;elementos relevantes comprovados&gt;"],
-  "lacunas": ["&lt;elementos obrigatórios ausentes ou insuficientes&gt;"],
-  "inconsistencias": ["&lt;incompatibilidades entre evidência, resposta declarada ou escopo&gt;"]
-}
-Regra de decisão binária:
-- Retorne "Conforme" somente quando a evidência for existente, compatível e suficiente para comprovar todos os elementos essenciais da avaliação descrita.
-- Retorne "Não conforme" quando a evidência for inexistente, ilegível, incompatível, desatualizada, meramente declaratória sem comprovação documental suficiente, ou quando faltar qualquer elemento essencial da avaliação.
-- Não use classificações intermediárias, como parcialmente conforme, parcialmente suficiente ou inconclusivo. Em caso de dúvida relevante, retorne "Não conforme" e descreva a lacuna.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:F38"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
